--- a/output/pdf_financials_xlsx/CSOC.A.xlsx
+++ b/output/pdf_financials_xlsx/CSOC.A.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.006902</v>
+        <v>0.127256</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.019027</v>
+        <v>0.263599</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.022315</v>
+        <v>0.238104</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.024515</v>
+        <v>0.56543</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.024821</v>
+        <v>0.336722</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.025536</v>
+        <v>0.347875</v>
       </c>
     </row>
     <row r="11">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1.993137</v>
+        <v>-2.113491</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.371636</v>
+        <v>-0.616208</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.7435890000000001</v>
+        <v>-0.959378</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3.102117</v>
+        <v>2.561202</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>12.707224</v>
+        <v>12.395323</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>18.114428</v>
+        <v>17.792089</v>
       </c>
     </row>
     <row r="12">
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011536</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.213304</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.137099</v>
       </c>
     </row>
     <row r="13">
@@ -1137,7 +1137,7 @@
         <v>-2.113491</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.616208</v>
+        <v>-0.627744</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.959378</v>
@@ -1146,10 +1146,10 @@
         <v>2.561202</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.395323</v>
+        <v>12.182019</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>17.792089</v>
+        <v>17.65499</v>
       </c>
     </row>
     <row r="28">
@@ -1187,7 +1187,7 @@
         <v>-2.113491</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.616208</v>
+        <v>-0.627744</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.959378</v>
@@ -1196,10 +1196,10 @@
         <v>2.561202</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12.395323</v>
+        <v>12.182019</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>17.792089</v>
+        <v>17.65499</v>
       </c>
     </row>
     <row r="30">
@@ -1212,7 +1212,7 @@
         <v>106.4068954579896</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>174.7567418869059</v>
+        <v>178.0283543528384</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>133.0115878293131</v>
@@ -1221,10 +1221,10 @@
         <v>81.9156843530035</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>97.3553188038528</v>
+        <v>95.67998699344842</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>98.08227293064088</v>
+        <v>97.32648863029716</v>
       </c>
     </row>
     <row r="31">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">

--- a/output/pdf_financials_xlsx/CSOC.A.xlsx
+++ b/output/pdf_financials_xlsx/CSOC.A.xlsx
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.006902</v>
+        <v>0.040387</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.019027</v>
+        <v>0.136997</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.022315</v>
+        <v>0.148836</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.024515</v>
+        <v>0.14962</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.024821</v>
+        <v>0.12479</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.025536</v>
+        <v>0.116823</v>
       </c>
     </row>
     <row r="8">
@@ -2053,19 +2053,19 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.032817</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.027361</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.169469</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.087047</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.14231</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -3334,22 +3334,22 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.289361</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.210035</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.850471</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.036539</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.522096</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>5.601414</v>
       </c>
     </row>
     <row r="116">
@@ -3744,10 +3744,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
@@ -3823,10 +3821,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.234915</v>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
@@ -3883,15 +3879,11 @@
       <c r="C135" s="3" t="n">
         <v>-0.189095</v>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>0.009506000000000001</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>0.147028</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.122176</v>
@@ -3911,7 +3903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6436,7 +6428,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.289361</v>
       </c>
@@ -6934,7 +6930,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -7066,7 +7066,11 @@
           <t>Net Cash Generated by Operating Activities</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -7651,72 +7655,76 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dividend income</t>
+          <t>Net Loss</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DividendIncome</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>-1.816593</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G86" s="5" t="n">
-        <v>0.003069</v>
-      </c>
-      <c r="H86" s="5" t="n">
-        <v>0.8386169999999999</v>
-      </c>
-      <c r="I86" s="5" t="n">
-        <v>1.394589</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>2.970748</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Proceeds on sale of investment</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0.289361</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7733,34 +7741,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n">
-        <v>0.213304</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>0.137099</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Realized gain on investments (Note 7)</t>
+          <t>Expenses paid by Canso Investment Counsel Ltd. on CSOC's behalf</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="5" t="n">
+        <v>0.050757</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7777,38 +7787,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="5" t="n">
-        <v>0.988314</v>
-      </c>
-      <c r="J88" s="5" t="n">
-        <v>2.794545</v>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Realized foreign exchange loss</t>
+          <t>Net Cash Provided by (used in) Operating Activities</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0.234915</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7825,38 +7837,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="5" t="n">
-        <v>-0.002024</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-0.01437</v>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Change in unrealized foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Issue of Class A Multiple Voting Share (Note 1)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>1e-05</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7873,34 +7883,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n">
-        <v>0.10837</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>0.09458</v>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Change in unrealized gain on investments (Note 7)</t>
+          <t>Class A Multiple Voting Share purchased for cancellation (Note 1)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E91" s="5" t="n">
+        <v>-1e-05</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7917,32 +7929,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n">
-        <v>10.029492</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>12.157362</v>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Total Income</t>
+          <t>Net Cash Provided by (used in) Financing Activities</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7955,80 +7971,102 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G92" s="5" t="n">
-        <v>-0.721274</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>3.126632</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>12.732045</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>18.139964</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Directors fees</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>0.033485</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>0.11797</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>0.126521</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>0.125105</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>0.099969</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>0.09128699999999999</v>
+          <t>Cash and cash equivalents — Beginning of period</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Professional fees (Note 6)</t>
+          <t>Cash and cash equivalents — End of period</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0.234915</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8045,11 +8083,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="5" t="n">
-        <v>0.133118</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>0.120467</v>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -8060,32 +8102,40 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>0.050481</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>0.042417</v>
+          <t>Dividend income</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DividendIncome</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.04587</v>
+        <v>0.003069</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0.10836</v>
+        <v>0.8386169999999999</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.078814</v>
+        <v>1.394589</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>0.110585</v>
+        <v>2.970748</v>
       </c>
     </row>
     <row r="96">
@@ -8096,36 +8146,44 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>0.000331</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>0.0007069999999999999</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>0.000982</v>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.001094</v>
+        <v>0.213304</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>0.001938</v>
+        <v>0.137099</v>
       </c>
     </row>
     <row r="97">
@@ -8136,36 +8194,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>0.006571</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>0.018227</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>0.021608</v>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>0.023533</v>
+          <t>Realized gain on investments (Note 7)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I97" s="5" t="n">
-        <v>0.023727</v>
+        <v>0.988314</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>0.023598</v>
+        <v>2.794545</v>
       </c>
     </row>
     <row r="98">
@@ -8176,36 +8238,44 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Realized foreign exchange loss</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>0.127256</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>0.263599</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>0.238104</v>
-      </c>
-      <c r="H98" s="5" t="n">
-        <v>0.56543</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.336722</v>
+        <v>-0.002024</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>0.347875</v>
+        <v>-0.01437</v>
       </c>
     </row>
     <row r="99">
@@ -8216,17 +8286,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Net Income before income taxes</t>
+          <t>Change in unrealized foreign exchange gain</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8244,14 +8314,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H99" s="5" t="n">
-        <v>2.561202</v>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>12.395323</v>
+        <v>0.10837</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>17.792089</v>
+        <v>0.09458</v>
       </c>
     </row>
     <row r="100">
@@ -8262,12 +8334,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Current (Note 8)</t>
+          <t>Change in unrealized gain on investments (Note 7)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -8291,13 +8363,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I100" s="5" t="n">
+        <v>10.029492</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>0.163292</v>
+        <v>12.157362</v>
       </c>
     </row>
     <row r="101">
@@ -8308,15 +8378,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Deferred (Note 8)</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -8327,21 +8401,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G101" s="5" t="n">
+        <v>-0.721274</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>3.126632</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>1.441195</v>
+        <v>12.732045</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>1.772779</v>
+        <v>18.139964</v>
       </c>
     </row>
     <row r="102">
@@ -8352,42 +8422,36 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Total Income Tax Expense</t>
+          <t>Directors fees</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0.033485</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.11797</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.126521</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.178032</v>
+        <v>0.125105</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>1.441195</v>
+        <v>0.099969</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>1.936071</v>
+        <v>0.09128699999999999</v>
       </c>
     </row>
     <row r="103">
@@ -8398,17 +8462,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income for the year</t>
+          <t>Professional fees (Note 6)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8426,14 +8490,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H103" s="5" t="n">
-        <v>2.38317</v>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I103" s="5" t="n">
-        <v>10.954128</v>
+        <v>0.133118</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>15.856018</v>
+        <v>0.120467</v>
       </c>
     </row>
     <row r="104">
@@ -8444,38 +8510,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Earnings per share attributable to shareholders</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="5" t="n">
+        <v>0.050481</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.042417</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.04587</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>4.6e-07</v>
+        <v>0.10836</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>2.1e-06</v>
+        <v>0.078814</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>3.04e-06</v>
+        <v>0.110585</v>
       </c>
     </row>
     <row r="105">
@@ -8486,38 +8546,36 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Earnings per share attributable to shareholders</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Diluted</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0.000331</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.0007069999999999999</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>4.6e-07</v>
+        <v>0.000982</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>2.1e-06</v>
+        <v>0.001094</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>3.04e-06</v>
+        <v>0.001938</v>
       </c>
     </row>
     <row r="106">
@@ -8528,40 +8586,36 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Interest income (expense)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0.006571</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0.018227</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.021608</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>-0.026359</v>
+        <v>0.023533</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.213304</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023727</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>0.023598</v>
       </c>
     </row>
     <row r="107">
@@ -8572,38 +8626,36 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Realized gain on investments (Note 8)</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>0.127256</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0.263599</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.446099</v>
+        <v>0.238104</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0.014283</v>
+        <v>0.56543</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0.988314</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.336722</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>0.347875</v>
       </c>
     </row>
     <row r="108">
@@ -8614,17 +8666,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Change in unrealized foreign exchange gain (loss)</t>
+          <t>Net Income before income taxes</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8643,15 +8695,13 @@
         </is>
       </c>
       <c r="H108" s="5" t="n">
-        <v>-0.051739</v>
+        <v>2.561202</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0.10837</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12.395323</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>17.792089</v>
       </c>
     </row>
     <row r="109">
@@ -8662,12 +8712,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Change in unrealized gain on investments (Note 8)</t>
+          <t>Current (Note 8)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8686,16 +8736,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H109" s="5" t="n">
-        <v>2.35183</v>
-      </c>
-      <c r="I109" s="5" t="n">
-        <v>10.029492</v>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>0.163292</v>
       </c>
     </row>
     <row r="110">
@@ -8706,19 +8758,15 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Professional fees (Note 7)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Deferred (Note 8)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -8729,19 +8777,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G110" s="5" t="n">
-        <v>0.043398</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>0.30745</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0.133118</v>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.441195</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>1.772779</v>
       </c>
     </row>
     <row r="111">
@@ -8757,10 +8807,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Deferred (Note 9)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Total Income Tax Expense</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -8782,10 +8836,8 @@
       <c r="I111" s="5" t="n">
         <v>1.441195</v>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J111" s="5" t="n">
+        <v>1.936071</v>
       </c>
     </row>
     <row r="112">
@@ -8796,15 +8848,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Interest (expense) income</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>Net income and comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -8815,21 +8871,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G112" s="5" t="n">
-        <v>0.030226</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>-0.026359</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.38317</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>10.954128</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>15.856018</v>
       </c>
     </row>
     <row r="113">
@@ -8840,19 +8894,15 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Earnings per share attributable to shareholders</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Change in unrealized foreign exchange (loss) gain</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -8863,21 +8913,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G113" s="5" t="n">
-        <v>0.08834699999999999</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>-0.051739</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.6e-07</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>2.1e-06</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>3.04e-06</v>
       </c>
     </row>
     <row r="114">
@@ -8888,12 +8936,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Earnings per share attributable to shareholders</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Change in unrealized gain (loss) on investments (Note 8)</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -8907,21 +8955,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G114" s="5" t="n">
-        <v>-1.289015</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H114" s="5" t="n">
-        <v>2.35183</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.6e-07</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>2.1e-06</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>3.04e-06</v>
       </c>
     </row>
     <row r="115">
@@ -8932,19 +8978,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Net Income (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Interest income (expense)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -8955,16 +8997,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" s="5" t="n">
-        <v>-0.959378</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>2.561202</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.026359</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0.213304</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -8980,12 +9022,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Deferred (Note 9)</t>
+          <t>Realized gain on investments (Note 8)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -9000,15 +9042,13 @@
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>-0.154906</v>
+        <v>0.446099</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0.178032</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014283</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>0.988314</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -9024,17 +9064,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Total Income Tax Expense (Recovery)</t>
+          <t>Change in unrealized foreign exchange gain (loss)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9047,16 +9087,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G117" s="5" t="n">
-        <v>-0.154906</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>0.178032</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.051739</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>0.10837</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -9072,19 +9112,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Change in unrealized gain on investments (Note 8)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -9095,16 +9131,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="5" t="n">
-        <v>-0.804472</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>2.38317</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.35183</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>10.029492</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -9120,15 +9156,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Net income (loss), by class</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Class A Multiple Voting Shares</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Professional fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -9140,15 +9180,13 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>-0.466624</v>
+        <v>0.043398</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>0.699574</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.30745</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>0.133118</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -9164,12 +9202,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Net income (loss), by class</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Class B Subordinate Voting Shares</t>
+          <t>Deferred (Note 9)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9183,16 +9221,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G120" s="5" t="n">
-        <v>-0.337848</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>1.683596</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.178032</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>1.441195</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -9208,12 +9246,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Net income (loss), per share</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Class A Multiple Voting Shares</t>
+          <t>Interest (expense) income</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9228,10 +9266,10 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>-2.9e-07</v>
+        <v>0.030226</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>4.6e-07</v>
+        <v>-0.026359</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -9252,15 +9290,19 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Net income (loss), per share</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Class B Subordinate Voting Shares</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Change in unrealized foreign exchange (loss) gain</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -9272,10 +9314,10 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>-2.9e-07</v>
+        <v>0.08834699999999999</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>4.6e-07</v>
+        <v>-0.051739</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -9296,36 +9338,30 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Change in unrealized gain (loss) on investments (Note 8)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F123" s="5" t="n">
-        <v>0.011536</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>-1.289015</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>2.35183</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -9346,30 +9382,34 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Realized loss on investment</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" s="5" t="n">
-        <v>-0.033768</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>-0.211033</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net Income (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>-0.959378</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>2.561202</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -9390,36 +9430,30 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Realized foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Deferred (Note 9)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F125" s="5" t="n">
-        <v>-0.00057</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>-0.154906</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>0.178032</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -9440,17 +9474,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Change in unrealized foreign exchange loss</t>
+          <t>Total Income Tax Expense (Recovery)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9458,18 +9492,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F126" s="5" t="n">
-        <v>-0.001101</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>-0.154906</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>0.178032</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -9490,30 +9522,34 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Change in unrealized loss on investment (Note 8)</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" s="5" t="n">
-        <v>-1.952467</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>-0.151441</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net income (loss) and comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>-0.804472</v>
+      </c>
+      <c r="H127" s="5" t="n">
+        <v>2.38317</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -9534,34 +9570,30 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Net income (loss), by class</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>-1.986235</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>-0.352609</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Class A Multiple Voting Shares</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>-0.466624</v>
+      </c>
+      <c r="H128" s="5" t="n">
+        <v>0.699574</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -9582,34 +9614,30 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income (loss), by class</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="n">
-        <v>0.036388</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>0.084185</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Class B Subordinate Voting Shares</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>-0.337848</v>
+      </c>
+      <c r="H129" s="5" t="n">
+        <v>1.683596</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -9630,34 +9658,30 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net income (loss), per share</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Net loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="n">
-        <v>-2.113491</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>-0.616208</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Class A Multiple Voting Shares</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>-2.9e-07</v>
+      </c>
+      <c r="H130" s="5" t="n">
+        <v>4.6e-07</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -9678,12 +9702,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Income taxes recovery</t>
+          <t>Net income (loss), per share</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Class B Subordinate Voting Shares</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -9697,15 +9721,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="5" t="n">
+        <v>-2.9e-07</v>
+      </c>
+      <c r="H131" s="5" t="n">
+        <v>4.6e-07</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -9726,20 +9746,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Income taxes recovery</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Deferred (Note 9)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" s="5" t="n">
-        <v>-0.296898</v>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.114134</v>
+        <v>0.011536</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -9770,20 +9796,20 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Income taxes recovery</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Total Income taxes recovery</t>
+          <t>Realized loss on investment</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" s="5" t="n">
-        <v>-0.296898</v>
+        <v>-0.033768</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>-0.114134</v>
+        <v>-0.211033</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -9814,24 +9840,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Income taxes recovery</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year/period</t>
+          <t>Realized foreign exchange loss</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>-1.816593</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.502074</v>
+        <v>-0.00057</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -9862,20 +9890,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Net loss, by class</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Class A Multiple Voting Shares</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" s="5" t="n">
-        <v>-1.060232</v>
+          <t>Change in unrealized foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F135" s="5" t="n">
-        <v>-0.293029</v>
+        <v>-0.001101</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -9906,20 +9940,20 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Net loss, by class</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Class B Subordinate Voting Shares</t>
+          <t>Change in unrealized loss on investment (Note 8)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" s="5" t="n">
-        <v>-0.756361</v>
+        <v>-1.952467</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>-0.209045</v>
+        <v>-0.151441</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -9950,20 +9984,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Net loss, per share</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Class A Multiple Voting Shares</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
-        <v>-6.5e-07</v>
+        <v>-1.986235</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>-1.8e-07</v>
+        <v>-0.352609</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -9994,37 +10032,1123 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>0.036388</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>0.084185</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Net loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>-2.113491</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>-0.616208</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Income taxes recovery</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Income taxes recovery</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Deferred (Note 9)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" s="5" t="n">
+        <v>-0.296898</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-0.114134</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Income taxes recovery</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Total Income taxes recovery</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>-0.296898</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>-0.114134</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Income taxes recovery</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year/period</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>-1.816593</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>-0.502074</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Net loss, by class</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Class A Multiple Voting Shares</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" s="5" t="n">
+        <v>-1.060232</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>-0.293029</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Net loss, by class</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Class B Subordinate Voting Shares</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" s="5" t="n">
+        <v>-0.756361</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>-0.209045</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
           <t>Net loss, per share</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Class A Multiple Voting Shares</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" s="5" t="n">
+        <v>-6.5e-07</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>-1.8e-07</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Net loss, per share</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Class B Subordinate Voting Shares</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="n">
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" s="5" t="n">
         <v>-6.5e-07</v>
       </c>
-      <c r="F138" s="5" t="n">
+      <c r="F147" s="5" t="n">
         <v>-1.8e-07</v>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Expenses (Notes 6 and</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" s="5" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Directors fees</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>0.033485</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" s="5" t="n">
+        <v>0.050481</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>0.000331</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>0.006571</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="n">
+        <v>0.036388</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>0.127256</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Net loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n">
+        <v>-2.113491</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Income taxes (Note</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" s="5" t="n">
+        <v>9e-06</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" s="5" t="n">
+        <v>0.296898</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="n">
+        <v>-1.816593</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Net loss, by class</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per Class A Multiple Voting Shares</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" s="5" t="n">
+        <v>-6.5e-07</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Net loss, by class</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per Class B Subordinate Voting Shares</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" s="5" t="n">
+        <v>-6.5e-07</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
